--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,772 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.4912,0.1176,0.0838,0.2693</t>
-  </si>
-  <si>
-    <t>0.0089,0.0002,0.0009,0.9962</t>
-  </si>
-  <si>
-    <t>0.9589,0.0133,0.0015,0.0186</t>
-  </si>
-  <si>
-    <t>0.0247,0.0016,0.0026,0.9900</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9825,0.0053,0.0002,0.0045</t>
-  </si>
-  <si>
-    <t>0.9909,0.0054,0.0015,0.0016</t>
-  </si>
-  <si>
-    <t>0.9956,0.0013,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9943,0.0016,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.8915,0.0397,0.0396,0.0088</t>
-  </si>
-  <si>
-    <t>0.0236,0.0138,0.9775,0.0032</t>
-  </si>
-  <si>
-    <t>0.1209,0.0261,0.8998,0.0024</t>
-  </si>
-  <si>
-    <t>0.0283,0.0124,0.9510,0.0033</t>
-  </si>
-  <si>
-    <t>0.9903,0.0016,0.0060,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.9980,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.9962,0.0059,0.0007</t>
-  </si>
-  <si>
-    <t>0.0161,0.9783,0.0012,0.0065</t>
-  </si>
-  <si>
-    <t>0.0009,0.9968,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.6752,0.0045,0.2874,0.0318</t>
-  </si>
-  <si>
-    <t>0.3623,0.0250,0.4984,0.0965</t>
-  </si>
-  <si>
-    <t>0.0338,0.0052,0.9588,0.0011</t>
-  </si>
-  <si>
-    <t>0.1020,0.0081,0.9360,0.0032</t>
-  </si>
-  <si>
-    <t>0.3647,0.0054,0.7521,0.0007</t>
-  </si>
-  <si>
-    <t>0.3030,0.0011,0.7991,0.0030</t>
-  </si>
-  <si>
-    <t>0.0089,0.0054,0.9841,0.0025</t>
-  </si>
-  <si>
-    <t>0.0546,0.9522,0.0080,0.0093</t>
-  </si>
-  <si>
-    <t>0.0710,0.8745,0.1008,0.0067</t>
-  </si>
-  <si>
-    <t>0.0042,0.0020,0.9945,0.0017</t>
-  </si>
-  <si>
-    <t>0.0091,0.9745,0.0154,0.0002</t>
-  </si>
-  <si>
-    <t>0.9051,0.0796,0.0076,0.0112</t>
-  </si>
-  <si>
-    <t>0.7505,0.0674,0.1340,0.0031</t>
-  </si>
-  <si>
-    <t>0.7156,0.4437,0.0098,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.9954,0.5541,0.0005</t>
-  </si>
-  <si>
-    <t>0.0411,0.4072,0.5077,0.0127</t>
-  </si>
-  <si>
-    <t>0.0435,0.0468,0.8805,0.0727</t>
-  </si>
-  <si>
-    <t>0.0419,0.0742,0.8628,0.0174</t>
-  </si>
-  <si>
-    <t>0.0214,0.0027,0.9802,0.0023</t>
-  </si>
-  <si>
-    <t>0.0554,0.0565,0.9610,0.0059</t>
-  </si>
-  <si>
-    <t>0.0062,0.9828,0.0149,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0051,0.9949,0.0127</t>
-  </si>
-  <si>
-    <t>0.0212,0.7829,0.0015,0.5242</t>
-  </si>
-  <si>
-    <t>0.0010,0.9936,0.0119,0.0158</t>
-  </si>
-  <si>
-    <t>0.0012,0.9952,0.0060,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9967,0.0051,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0022,0.9974,0.0025</t>
-  </si>
-  <si>
-    <t>0.0016,0.8904,0.9853,0.0008</t>
-  </si>
-  <si>
-    <t>0.0439,0.1454,0.9214,0.0094</t>
-  </si>
-  <si>
-    <t>0.0390,0.0007,0.9710,0.0023</t>
-  </si>
-  <si>
-    <t>0.0004,0.0050,0.9981,0.0011</t>
-  </si>
-  <si>
-    <t>0.0037,0.0289,0.9888,0.0012</t>
-  </si>
-  <si>
-    <t>0.9772,0.0440,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9870,0.0066,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.9932,0.0024,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.0031,0.0188,0.9967,0.0030</t>
-  </si>
-  <si>
-    <t>0.9932,0.0028,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9919,0.0088,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9860,0.0122,0.0012,0.0016</t>
-  </si>
-  <si>
-    <t>0.0069,0.8637,0.9555,0.0019</t>
-  </si>
-  <si>
-    <t>0.0025,0.0148,0.9944,0.0046</t>
-  </si>
-  <si>
-    <t>0.0027,0.0184,0.9775,0.0112</t>
-  </si>
-  <si>
-    <t>0.0005,0.7348,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0015,0.9929,0.0041</t>
-  </si>
-  <si>
-    <t>0.0235,0.9763,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.9920,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.9372,0.0112,0.0803,0.0032</t>
-  </si>
-  <si>
-    <t>0.8829,0.1092,0.0201,0.0058</t>
-  </si>
-  <si>
-    <t>0.0036,0.0231,0.9897,0.0074</t>
-  </si>
-  <si>
-    <t>0.0088,0.6230,0.8057,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.9633,0.8687,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9974,0.5447,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9901,0.9755,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.0004,0.0137,0.9963</t>
-  </si>
-  <si>
-    <t>0.0004,0.0021,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0026,0.0037,0.0027,0.9963</t>
-  </si>
-  <si>
-    <t>0.0142,0.0038,0.0051,0.9887</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.0010,0.9991</t>
-  </si>
-  <si>
-    <t>0.0075,0.0052,0.0064,0.9910</t>
-  </si>
-  <si>
-    <t>0.0008,0.9910,0.8400,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9488,0.9751,0.0005</t>
-  </si>
-  <si>
-    <t>0.0023,0.9720,0.6088,0.0021</t>
-  </si>
-  <si>
-    <t>0.0005,0.9096,0.9901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9591,0.9414,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.6234,0.9676,0.0008</t>
-  </si>
-  <si>
-    <t>0.9964,0.0017,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9815,0.0092,0.0080,0.0011</t>
-  </si>
-  <si>
-    <t>0.9935,0.0078,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9862,0.0211,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0092,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0017,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9948,0.0014,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.9892,0.0081,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9939,0.0023,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.0015,0.0028,0.9959,0.0034</t>
-  </si>
-  <si>
-    <t>0.0110,0.0041,0.9787,0.0073</t>
-  </si>
-  <si>
-    <t>0.9848,0.0042,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.0461,0.0110,0.9283,0.0091</t>
-  </si>
-  <si>
-    <t>0.0056,0.9928,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.0036,0.9949,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.0048,0.9894,0.0027,0.0053</t>
-  </si>
-  <si>
-    <t>0.0018,0.9959,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.0027,0.9951,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.0024,0.9948,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.4209,0.6333,0.0023,0.0067</t>
-  </si>
-  <si>
-    <t>0.7906,0.1059,0.1313,0.0078</t>
-  </si>
-  <si>
-    <t>0.1032,0.0527,0.8700,0.0075</t>
-  </si>
-  <si>
-    <t>0.7484,0.0315,0.2052,0.0258</t>
-  </si>
-  <si>
-    <t>0.6419,0.0767,0.2956,0.0105</t>
-  </si>
-  <si>
-    <t>0.0164,0.1376,0.0118,0.9368</t>
-  </si>
-  <si>
-    <t>0.0051,0.9848,0.0197,0.0075</t>
-  </si>
-  <si>
-    <t>0.0005,0.9966,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.9935,0.0021,0.0059</t>
-  </si>
-  <si>
-    <t>0.0022,0.9721,0.8144,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.9960,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.8705,0.1766,0.0058,0.0018</t>
-  </si>
-  <si>
-    <t>0.6343,0.3998,0.0124,0.0016</t>
-  </si>
-  <si>
-    <t>0.9944,0.0027,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9909,0.0044,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9919,0.0017,0.0015,0.0028</t>
-  </si>
-  <si>
-    <t>0.9733,0.0064,0.0068,0.0093</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0012,0.0009,0.0029</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9365,0.9853,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.8575,0.9575,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.0505,0.9809,0.0003</t>
-  </si>
-  <si>
-    <t>0.0086,0.0300,0.9782,0.0002</t>
-  </si>
-  <si>
-    <t>0.9879,0.0024,0.0021,0.0013</t>
-  </si>
-  <si>
-    <t>0.8367,0.0351,0.1218,0.0029</t>
-  </si>
-  <si>
-    <t>0.6032,0.0043,0.4953,0.0135</t>
-  </si>
-  <si>
-    <t>0.9367,0.0070,0.0644,0.0064</t>
-  </si>
-  <si>
-    <t>0.3946,0.0012,0.0007,0.8479</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0017,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.0007,0.9997</t>
-  </si>
-  <si>
-    <t>0.0055,0.0001,0.0003,0.9981</t>
-  </si>
-  <si>
-    <t>0.0015,0.9749,0.3389,0.0005</t>
-  </si>
-  <si>
-    <t>0.9897,0.0071,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.0122,0.9721,0.0006,0.0384</t>
-  </si>
-  <si>
-    <t>0.9936,0.0007,0.0003,0.0047</t>
-  </si>
-  <si>
-    <t>0.3907,0.6603,0.0011,0.0094</t>
-  </si>
-  <si>
-    <t>0.9960,0.0014,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.8145,0.0119,0.0219,0.2497</t>
-  </si>
-  <si>
-    <t>0.9948,0.0015,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0045,0.1281,0.9793,0.0601</t>
-  </si>
-  <si>
-    <t>0.9906,0.0008,0.0009,0.0062</t>
-  </si>
-  <si>
-    <t>0.9178,0.0021,0.0072,0.1279</t>
-  </si>
-  <si>
-    <t>0.8360,0.1141,0.0494,0.0098</t>
-  </si>
-  <si>
-    <t>0.9706,0.0210,0.0029,0.0031</t>
-  </si>
-  <si>
-    <t>0.9177,0.0526,0.0177,0.0034</t>
-  </si>
-  <si>
-    <t>0.2160,0.8163,0.0076,0.0033</t>
-  </si>
-  <si>
-    <t>0.9523,0.0279,0.0122,0.0021</t>
-  </si>
-  <si>
-    <t>0.9536,0.0207,0.0139,0.0035</t>
-  </si>
-  <si>
-    <t>0.9728,0.0123,0.0016,0.0091</t>
-  </si>
-  <si>
-    <t>0.9871,0.0144,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9942,0.0011,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9852,0.0030,0.0007,0.0098</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9803,0.0201,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9970,0.0005,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9968,0.0009,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9599,0.0470,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.6429,0.5122,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.4820,0.6453,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.7536,0.1963,0.0297,0.0269</t>
-  </si>
-  <si>
-    <t>0.9732,0.0601,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9510,0.0582,0.0043,0.0036</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.7108,0.4118,0.0084,0.0032</t>
-  </si>
-  <si>
-    <t>0.0050,0.0058,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.9107,0.0555,0.0276,0.0013</t>
-  </si>
-  <si>
-    <t>0.0164,0.0050,0.9810,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0512,0.9883,0.0030</t>
-  </si>
-  <si>
-    <t>0.0037,0.0009,0.9942,0.0010</t>
-  </si>
-  <si>
-    <t>0.0058,0.1864,0.9843,0.0007</t>
-  </si>
-  <si>
-    <t>0.0104,0.0069,0.9850,0.0015</t>
-  </si>
-  <si>
-    <t>0.0050,0.0014,0.9941,0.0013</t>
-  </si>
-  <si>
-    <t>0.0033,0.0064,0.9958,0.0005</t>
-  </si>
-  <si>
-    <t>0.0529,0.0120,0.9497,0.0010</t>
-  </si>
-  <si>
-    <t>0.4050,0.0366,0.6427,0.0136</t>
-  </si>
-  <si>
-    <t>0.2555,0.0237,0.7979,0.0052</t>
-  </si>
-  <si>
-    <t>0.1010,0.3770,0.5363,0.0101</t>
-  </si>
-  <si>
-    <t>0.0083,0.9090,0.1618,0.0004</t>
-  </si>
-  <si>
-    <t>0.3140,0.0037,0.7919,0.0011</t>
-  </si>
-  <si>
-    <t>0.9145,0.0303,0.0325,0.0151</t>
-  </si>
-  <si>
-    <t>0.0791,0.0023,0.9391,0.0026</t>
-  </si>
-  <si>
-    <t>0.3784,0.7934,0.0044,0.0009</t>
-  </si>
-  <si>
-    <t>0.0839,0.9408,0.0107,0.0014</t>
-  </si>
-  <si>
-    <t>0.4247,0.7452,0.0069,0.0009</t>
-  </si>
-  <si>
-    <t>0.8097,0.3288,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.0108,0.9886,0.0013,0.0023</t>
-  </si>
-  <si>
-    <t>0.8009,0.2169,0.0092,0.0027</t>
-  </si>
-  <si>
-    <t>0.9793,0.0014,0.0163,0.0010</t>
-  </si>
-  <si>
-    <t>0.9650,0.0119,0.0107,0.0030</t>
-  </si>
-  <si>
-    <t>0.3512,0.0139,0.6962,0.0186</t>
-  </si>
-  <si>
-    <t>0.8151,0.0074,0.1179,0.0470</t>
-  </si>
-  <si>
-    <t>0.0176,0.0037,0.9849,0.0020</t>
-  </si>
-  <si>
-    <t>0.0058,0.0752,0.9531,0.0063</t>
-  </si>
-  <si>
-    <t>0.0468,0.0325,0.9523,0.0020</t>
-  </si>
-  <si>
-    <t>0.0514,0.1421,0.7881,0.0043</t>
-  </si>
-  <si>
-    <t>0.0045,0.0816,0.9627,0.0003</t>
-  </si>
-  <si>
-    <t>0.9812,0.0031,0.0003,0.0125</t>
-  </si>
-  <si>
-    <t>0.9930,0.0019,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9920,0.0057,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.9860,0.0161,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9796,0.0187,0.0029,0.0019</t>
-  </si>
-  <si>
-    <t>0.9875,0.0078,0.0019,0.0027</t>
-  </si>
-  <si>
-    <t>0.9786,0.0148,0.0028,0.0046</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0212,0.0417,0.9870,0.0011</t>
-  </si>
-  <si>
-    <t>0.4326,0.2414,0.3666,0.0127</t>
-  </si>
-  <si>
-    <t>0.9658,0.0038,0.0056,0.0242</t>
-  </si>
-  <si>
-    <t>0.0102,0.0139,0.9845,0.0044</t>
-  </si>
-  <si>
-    <t>0.0010,0.2762,0.9961,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.1284,0.9850,0.0009</t>
-  </si>
-  <si>
-    <t>0.0134,0.0015,0.9925,0.0003</t>
-  </si>
-  <si>
-    <t>0.0809,0.0290,0.8665,0.0111</t>
-  </si>
-  <si>
-    <t>0.0152,0.0064,0.9816,0.0047</t>
-  </si>
-  <si>
-    <t>0.0076,0.0726,0.9729,0.0033</t>
-  </si>
-  <si>
-    <t>0.0140,0.0656,0.9491,0.0048</t>
-  </si>
-  <si>
-    <t>0.9603,0.0011,0.0554,0.0010</t>
-  </si>
-  <si>
-    <t>0.8536,0.0047,0.2430,0.0021</t>
-  </si>
-  <si>
-    <t>0.9660,0.0042,0.0141,0.0071</t>
-  </si>
-  <si>
-    <t>0.9969,0.0013,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9926,0.0093,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9949,0.0022,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9937,0.0063,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9920,0.0082,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.0235,0.0259,0.9576,0.0048</t>
-  </si>
-  <si>
-    <t>0.0025,0.0049,0.9940,0.0010</t>
-  </si>
-  <si>
-    <t>0.0039,0.0052,0.9899,0.0014</t>
-  </si>
-  <si>
-    <t>0.0063,0.6936,0.5475,0.0007</t>
-  </si>
-  <si>
-    <t>0.0132,0.0098,0.9840,0.0025</t>
-  </si>
-  <si>
-    <t>0.1702,0.0347,0.8107,0.0579</t>
-  </si>
-  <si>
-    <t>0.0867,0.0017,0.9531,0.0013</t>
-  </si>
-  <si>
-    <t>0.0095,0.0037,0.9737,0.0086</t>
-  </si>
-  <si>
-    <t>0.9957,0.0003,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.0033,0.2788,0.0007,0.9889</t>
-  </si>
-  <si>
-    <t>0.0710,0.0047,0.0004,0.9751</t>
-  </si>
-  <si>
-    <t>0.0080,0.0008,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.9506,0.0047,0.0058,0.0502</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9753,0.0043,0.0085,0.0072</t>
+  </si>
+  <si>
+    <t>0.0202,0.0004,0.0001,0.9954</t>
+  </si>
+  <si>
+    <t>0.9527,0.0024,0.0007,0.0522</t>
+  </si>
+  <si>
+    <t>0.1998,0.0019,0.0002,0.9371</t>
+  </si>
+  <si>
+    <t>0.9964,0.0019,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0007,0.0011,0.0036</t>
+  </si>
+  <si>
+    <t>0.9932,0.0056,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9869,0.0125,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0021,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.7944,0.0783,0.0748,0.0454</t>
+  </si>
+  <si>
+    <t>0.2592,0.0111,0.8545,0.0005</t>
+  </si>
+  <si>
+    <t>0.1439,0.0247,0.8755,0.0034</t>
+  </si>
+  <si>
+    <t>0.0171,0.0076,0.9791,0.0006</t>
+  </si>
+  <si>
+    <t>0.9801,0.0031,0.0113,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0060,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.9946,0.0083,0.0017</t>
+  </si>
+  <si>
+    <t>0.0155,0.9795,0.0006,0.0046</t>
+  </si>
+  <si>
+    <t>0.0025,0.9923,0.0213,0.0017</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.8803,0.0073,0.0688,0.0365</t>
+  </si>
+  <si>
+    <t>0.4911,0.0134,0.4919,0.0311</t>
+  </si>
+  <si>
+    <t>0.0099,0.0054,0.9838,0.0008</t>
+  </si>
+  <si>
+    <t>0.0795,0.0781,0.8005,0.0045</t>
+  </si>
+  <si>
+    <t>0.1374,0.0221,0.8454,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.9935,0.0011</t>
+  </si>
+  <si>
+    <t>0.0121,0.0040,0.9689,0.0333</t>
+  </si>
+  <si>
+    <t>0.3783,0.7143,0.0181,0.0064</t>
+  </si>
+  <si>
+    <t>0.2330,0.4199,0.4264,0.0048</t>
+  </si>
+  <si>
+    <t>0.0012,0.0055,0.9949,0.0079</t>
+  </si>
+  <si>
+    <t>0.0105,0.9800,0.0082,0.0002</t>
+  </si>
+  <si>
+    <t>0.9766,0.0229,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9722,0.0095,0.0117,0.0020</t>
+  </si>
+  <si>
+    <t>0.7631,0.3712,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.9949,0.1108,0.0008</t>
+  </si>
+  <si>
+    <t>0.0167,0.5184,0.5521,0.0295</t>
+  </si>
+  <si>
+    <t>0.0275,0.7829,0.7508,0.0130</t>
+  </si>
+  <si>
+    <t>0.0234,0.0340,0.9587,0.0082</t>
+  </si>
+  <si>
+    <t>0.1770,0.0032,0.8698,0.0025</t>
+  </si>
+  <si>
+    <t>0.0193,0.3558,0.9634,0.0024</t>
+  </si>
+  <si>
+    <t>0.0014,0.9943,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0106,0.9905,0.0162</t>
+  </si>
+  <si>
+    <t>0.2583,0.6128,0.1809,0.1771</t>
+  </si>
+  <si>
+    <t>0.0037,0.9837,0.0175,0.0114</t>
+  </si>
+  <si>
+    <t>0.0010,0.9940,0.0201,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0135,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0054,0.9978,0.0025</t>
+  </si>
+  <si>
+    <t>0.0004,0.6946,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0142,0.0045,0.9840,0.0010</t>
+  </si>
+  <si>
+    <t>0.0177,0.0008,0.9842,0.0015</t>
+  </si>
+  <si>
+    <t>0.0088,0.0114,0.9869,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.0039,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0147,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9795,0.0043,0.0077,0.0061</t>
+  </si>
+  <si>
+    <t>0.9828,0.0090,0.0028,0.0030</t>
+  </si>
+  <si>
+    <t>0.0027,0.0123,0.9962,0.0056</t>
+  </si>
+  <si>
+    <t>0.9563,0.0418,0.0063,0.0047</t>
+  </si>
+  <si>
+    <t>0.9955,0.0043,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9914,0.0056,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9654,0.9824,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.1145,0.9928,0.0032</t>
+  </si>
+  <si>
+    <t>0.0021,0.0044,0.9288,0.1292</t>
+  </si>
+  <si>
+    <t>0.0007,0.9524,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0096,0.0088,0.9910,0.0006</t>
+  </si>
+  <si>
+    <t>0.0282,0.9673,0.0102,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9968,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9614,0.0014,0.0726,0.0006</t>
+  </si>
+  <si>
+    <t>0.0512,0.2856,0.8763,0.0110</t>
+  </si>
+  <si>
+    <t>0.0030,0.0110,0.9953,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9756,0.9634,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9943,0.0290,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9956,0.3464,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.9729,0.9791,0.0004</t>
+  </si>
+  <si>
+    <t>0.0149,0.0003,0.0008,0.9952</t>
+  </si>
+  <si>
+    <t>0.0061,0.0029,0.0013,0.9958</t>
+  </si>
+  <si>
+    <t>0.0010,0.0032,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0096,0.0028,0.0015,0.9941</t>
+  </si>
+  <si>
+    <t>0.0062,0.0010,0.0046,0.9954</t>
+  </si>
+  <si>
+    <t>0.0011,0.0009,0.0010,0.9989</t>
+  </si>
+  <si>
+    <t>0.0025,0.9418,0.9468,0.0007</t>
+  </si>
+  <si>
+    <t>0.0015,0.9730,0.9604,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.9762,0.7530,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.3821,0.9842,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9969,0.7893,0.0002</t>
+  </si>
+  <si>
+    <t>0.0131,0.4192,0.9369,0.0016</t>
+  </si>
+  <si>
+    <t>0.9960,0.0032,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0038,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.9856,0.0159,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9857,0.0138,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9923,0.0034,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9809,0.0128,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.9971,0.0013,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9926,0.0046,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9972,0.0011,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0026,0.0032,0.9948,0.0034</t>
+  </si>
+  <si>
+    <t>0.0036,0.0114,0.9845,0.0062</t>
+  </si>
+  <si>
+    <t>0.9449,0.0104,0.0113,0.0217</t>
+  </si>
+  <si>
+    <t>0.0051,0.0009,0.9829,0.0075</t>
+  </si>
+  <si>
+    <t>0.0163,0.9809,0.0009,0.0038</t>
+  </si>
+  <si>
+    <t>0.0015,0.9966,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0038,0.9905,0.0029,0.0050</t>
+  </si>
+  <si>
+    <t>0.0676,0.9415,0.0117,0.0054</t>
+  </si>
+  <si>
+    <t>0.0069,0.9882,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.0046,0.9920,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.2651,0.8066,0.0057,0.0040</t>
+  </si>
+  <si>
+    <t>0.4179,0.1109,0.4846,0.0106</t>
+  </si>
+  <si>
+    <t>0.1028,0.0175,0.8944,0.0032</t>
+  </si>
+  <si>
+    <t>0.2645,0.2973,0.2973,0.0126</t>
+  </si>
+  <si>
+    <t>0.2886,0.0126,0.7531,0.0018</t>
+  </si>
+  <si>
+    <t>0.0286,0.0621,0.0203,0.9244</t>
+  </si>
+  <si>
+    <t>0.0007,0.9965,0.0060,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.9723,0.0002,0.0427</t>
+  </si>
+  <si>
+    <t>0.0036,0.9220,0.7144,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.9941,0.0148,0.0003</t>
+  </si>
+  <si>
+    <t>0.7727,0.3262,0.0071,0.0020</t>
+  </si>
+  <si>
+    <t>0.9115,0.1145,0.0057,0.0017</t>
+  </si>
+  <si>
+    <t>0.9892,0.0120,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9811,0.0051,0.0022,0.0129</t>
+  </si>
+  <si>
+    <t>0.9956,0.0015,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0019,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0009,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.0016,0.7209,0.9725,0.0015</t>
+  </si>
+  <si>
+    <t>0.0061,0.3415,0.9506,0.0001</t>
+  </si>
+  <si>
+    <t>0.0099,0.0121,0.9850,0.0003</t>
+  </si>
+  <si>
+    <t>0.0236,0.0114,0.9829,0.0014</t>
+  </si>
+  <si>
+    <t>0.9854,0.0021,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.9629,0.0068,0.0231,0.0032</t>
+  </si>
+  <si>
+    <t>0.0632,0.0039,0.9650,0.0020</t>
+  </si>
+  <si>
+    <t>0.8580,0.0351,0.1125,0.0209</t>
+  </si>
+  <si>
+    <t>0.1195,0.0041,0.0009,0.9521</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0016,0.9999</t>
+  </si>
+  <si>
+    <t>0.0012,0.0151,0.0049,0.9969</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0013,0.9992</t>
+  </si>
+  <si>
+    <t>0.0031,0.8211,0.8228,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0129,0.9829,0.0003,0.0042</t>
+  </si>
+  <si>
+    <t>0.9931,0.0021,0.0004,0.0023</t>
+  </si>
+  <si>
+    <t>0.3753,0.7078,0.0032,0.0043</t>
+  </si>
+  <si>
+    <t>0.9901,0.0019,0.0038,0.0008</t>
+  </si>
+  <si>
+    <t>0.9731,0.0032,0.0017,0.0336</t>
+  </si>
+  <si>
+    <t>0.9672,0.0048,0.0111,0.0092</t>
+  </si>
+  <si>
+    <t>0.0150,0.1334,0.9693,0.0456</t>
+  </si>
+  <si>
+    <t>0.9638,0.0005,0.0044,0.0174</t>
+  </si>
+  <si>
+    <t>0.9827,0.0007,0.0035,0.0113</t>
+  </si>
+  <si>
+    <t>0.2426,0.7832,0.0145,0.0049</t>
+  </si>
+  <si>
+    <t>0.9901,0.0064,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9563,0.0079,0.0313,0.0034</t>
+  </si>
+  <si>
+    <t>0.1506,0.7260,0.1095,0.0187</t>
+  </si>
+  <si>
+    <t>0.9079,0.1014,0.0053,0.0018</t>
+  </si>
+  <si>
+    <t>0.8699,0.0960,0.0249,0.0024</t>
+  </si>
+  <si>
+    <t>0.9884,0.0041,0.0016,0.0029</t>
+  </si>
+  <si>
+    <t>0.9948,0.0033,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9888,0.0046,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9858,0.0126,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0013,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9677,0.0290,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.6714,0.4321,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.2708,0.8202,0.0029,0.0036</t>
+  </si>
+  <si>
+    <t>0.8138,0.1284,0.1033,0.0205</t>
+  </si>
+  <si>
+    <t>0.8694,0.2332,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9126,0.0947,0.0031,0.0066</t>
+  </si>
+  <si>
+    <t>0.9931,0.0082,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.1832,0.8937,0.0038,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.0280,0.9988,0.0010</t>
+  </si>
+  <si>
+    <t>0.9795,0.0103,0.0085,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.0044,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.0083,0.0277,0.9793,0.0042</t>
+  </si>
+  <si>
+    <t>0.0034,0.0018,0.9950,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.2424,0.9924,0.0002</t>
+  </si>
+  <si>
+    <t>0.0226,0.0088,0.9876,0.0013</t>
+  </si>
+  <si>
+    <t>0.0346,0.0014,0.9773,0.0002</t>
+  </si>
+  <si>
+    <t>0.0093,0.0048,0.9908,0.0012</t>
+  </si>
+  <si>
+    <t>0.0422,0.0045,0.9714,0.0014</t>
+  </si>
+  <si>
+    <t>0.8410,0.0513,0.1429,0.0207</t>
+  </si>
+  <si>
+    <t>0.0799,0.0149,0.9259,0.0022</t>
+  </si>
+  <si>
+    <t>0.2209,0.0603,0.7719,0.0077</t>
+  </si>
+  <si>
+    <t>0.2097,0.0438,0.7517,0.0016</t>
+  </si>
+  <si>
+    <t>0.6716,0.0044,0.4690,0.0003</t>
+  </si>
+  <si>
+    <t>0.6303,0.0418,0.2886,0.0853</t>
+  </si>
+  <si>
+    <t>0.4446,0.0290,0.5996,0.0056</t>
+  </si>
+  <si>
+    <t>0.0403,0.9621,0.0131,0.0012</t>
+  </si>
+  <si>
+    <t>0.0843,0.9584,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.9308,0.1013,0.0042,0.0019</t>
+  </si>
+  <si>
+    <t>0.8935,0.2702,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0329,0.9703,0.0030,0.0020</t>
+  </si>
+  <si>
+    <t>0.9722,0.0197,0.0019,0.0015</t>
+  </si>
+  <si>
+    <t>0.9848,0.0006,0.0119,0.0007</t>
+  </si>
+  <si>
+    <t>0.9063,0.0267,0.0405,0.0222</t>
+  </si>
+  <si>
+    <t>0.6938,0.0108,0.3128,0.0358</t>
+  </si>
+  <si>
+    <t>0.6763,0.0157,0.3779,0.0061</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9968,0.0089</t>
+  </si>
+  <si>
+    <t>0.0836,0.0174,0.8607,0.0209</t>
+  </si>
+  <si>
+    <t>0.0374,0.0206,0.9649,0.0015</t>
+  </si>
+  <si>
+    <t>0.1122,0.0069,0.9225,0.0011</t>
+  </si>
+  <si>
+    <t>0.0075,0.0826,0.9602,0.0011</t>
+  </si>
+  <si>
+    <t>0.9950,0.0022,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9946,0.0026,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0049,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9894,0.0061,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9565,0.0289,0.0025,0.0087</t>
+  </si>
+  <si>
+    <t>0.9894,0.0031,0.0005,0.0050</t>
+  </si>
+  <si>
+    <t>0.9940,0.0024,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.0411,0.0180,0.9647,0.0044</t>
+  </si>
+  <si>
+    <t>0.3986,0.1644,0.4995,0.0208</t>
+  </si>
+  <si>
+    <t>0.8772,0.0061,0.0892,0.0137</t>
+  </si>
+  <si>
+    <t>0.0035,0.0355,0.9897,0.0026</t>
+  </si>
+  <si>
+    <t>0.0035,0.0112,0.9886,0.0029</t>
+  </si>
+  <si>
+    <t>0.0040,0.2202,0.9504,0.0006</t>
+  </si>
+  <si>
+    <t>0.0040,0.0022,0.9956,0.0005</t>
+  </si>
+  <si>
+    <t>0.0101,0.0243,0.9693,0.0050</t>
+  </si>
+  <si>
+    <t>0.0028,0.0052,0.9906,0.0074</t>
+  </si>
+  <si>
+    <t>0.0046,0.0068,0.9895,0.0010</t>
+  </si>
+  <si>
+    <t>0.1675,0.4450,0.3726,0.0201</t>
+  </si>
+  <si>
+    <t>0.4260,0.0014,0.7777,0.0013</t>
+  </si>
+  <si>
+    <t>0.6475,0.0157,0.4669,0.0062</t>
+  </si>
+  <si>
+    <t>0.7806,0.0486,0.0840,0.1077</t>
+  </si>
+  <si>
+    <t>0.9685,0.0184,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9933,0.0089,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9895,0.0070,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9911,0.0082,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0056,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.0198,0.1846,0.7838,0.0073</t>
+  </si>
+  <si>
+    <t>0.0028,0.0159,0.9931,0.0008</t>
+  </si>
+  <si>
+    <t>0.0106,0.0505,0.9563,0.0069</t>
+  </si>
+  <si>
+    <t>0.0271,0.2731,0.6766,0.0079</t>
+  </si>
+  <si>
+    <t>0.0062,0.0059,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0864,0.0237,0.8425,0.0877</t>
+  </si>
+  <si>
+    <t>0.1953,0.0123,0.8398,0.0122</t>
+  </si>
+  <si>
+    <t>0.0090,0.0078,0.9427,0.0440</t>
+  </si>
+  <si>
+    <t>0.9805,0.0005,0.0019,0.0136</t>
+  </si>
+  <si>
+    <t>0.0015,0.1494,0.0005,0.9955</t>
+  </si>
+  <si>
+    <t>0.0470,0.0058,0.0004,0.9836</t>
+  </si>
+  <si>
+    <t>0.0033,0.0037,0.0027,0.9968</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.0006,0.9986</t>
+  </si>
+  <si>
+    <t>0.9871,0.0024,0.0010,0.0087</t>
   </si>
 </sst>
 </file>
@@ -2278,7 +2278,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
         <v>288</v>
@@ -2376,7 +2376,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
         <v>295</v>
@@ -2460,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>301</v>
@@ -2474,7 +2474,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>302</v>
@@ -2488,7 +2488,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D40" t="s">
         <v>303</v>
@@ -2572,7 +2572,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>309</v>
@@ -2922,7 +2922,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>334</v>
@@ -2964,7 +2964,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>337</v>
@@ -2978,7 +2978,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>338</v>
@@ -3132,7 +3132,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>349</v>
@@ -3160,7 +3160,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
         <v>351</v>
@@ -3552,7 +3552,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
         <v>379</v>
@@ -3580,7 +3580,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
         <v>381</v>
@@ -3594,7 +3594,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>382</v>
@@ -3846,7 +3846,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>400</v>
@@ -3916,7 +3916,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>405</v>
@@ -4000,7 +4000,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>411</v>
@@ -4154,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>422</v>
@@ -4364,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
         <v>437</v>
@@ -4448,7 +4448,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
         <v>443</v>
@@ -4602,7 +4602,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>454</v>
@@ -4644,7 +4644,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>457</v>
@@ -4658,7 +4658,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>458</v>
@@ -4728,7 +4728,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
         <v>463</v>
@@ -4812,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
         <v>469</v>
@@ -5036,7 +5036,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
         <v>485</v>
@@ -5162,7 +5162,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
         <v>494</v>
@@ -5176,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
         <v>495</v>
@@ -5372,7 +5372,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>509</v>
